--- a/artfynd/S 2477-2025 artfynd.xlsx
+++ b/artfynd/S 2477-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6741390</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58207215</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89362212</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1178,6 +1198,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89362222</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1324,6 +1349,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89362220</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1450,6 +1480,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89362236</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1561,6 +1596,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91523081</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1707,6 +1747,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89362221</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1848,6 +1893,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89362216</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1984,6 +2034,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89362206</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2090,6 +2145,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2145710</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2196,6 +2256,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2154422</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2302,6 +2367,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2156424</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2408,6 +2478,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2209065</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2514,6 +2589,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2311092</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2620,6 +2700,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2311431</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2726,6 +2811,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2592126</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2832,6 +2922,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2592653</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2947,6 +3042,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2764339</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3062,6 +3162,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2764799</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3168,6 +3273,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3456983</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3274,6 +3384,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3255848</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3380,6 +3495,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4239371</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3495,6 +3615,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4816430</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3611,6 +3736,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4948268</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3717,6 +3847,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5044010</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3832,6 +3967,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91523184</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3934,6 +4074,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5900256</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4036,8 +4181,44 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5980519</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>